--- a/艾迪英特請假單_template.xlsx
+++ b/艾迪英特請假單_template.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="PMingLiu"/>
       <color rgb="FF000000"/>
@@ -43,6 +43,10 @@
       <name val="PMingLiu"/>
       <color theme="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="DFKai-SB"/>
+      <sz val="16"/>
     </font>
   </fonts>
   <fills count="2">
@@ -185,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -271,6 +275,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -598,20 +605,11 @@
       <c r="Z1" s="2" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1" s="28">
-      <c r="A2" s="2" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>請假單</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
@@ -702,28 +700,28 @@
       <c r="Z4" s="2" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="28">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>請假人：</t>
         </is>
       </c>
-      <c r="B5" s="30" t="n"/>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="31" t="n"/>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="32" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
+      <c r="H5" s="30" t="inlineStr">
         <is>
           <t>代理人：</t>
         </is>
       </c>
-      <c r="I5" s="30" t="n"/>
-      <c r="J5" s="31" t="n"/>
-      <c r="K5" s="29" t="n"/>
-      <c r="L5" s="30" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="31" t="n"/>
+      <c r="I5" s="31" t="n"/>
+      <c r="J5" s="32" t="n"/>
+      <c r="K5" s="30" t="n"/>
+      <c r="L5" s="31" t="n"/>
+      <c r="M5" s="31" t="n"/>
+      <c r="N5" s="32" t="n"/>
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="n"/>
@@ -738,20 +736,20 @@
       <c r="Z5" s="2" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="28">
-      <c r="A6" s="32" t="n"/>
-      <c r="B6" s="33" t="n"/>
-      <c r="C6" s="34" t="n"/>
-      <c r="D6" s="32" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="33" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="32" t="n"/>
-      <c r="I6" s="33" t="n"/>
-      <c r="J6" s="34" t="n"/>
-      <c r="K6" s="32" t="n"/>
-      <c r="L6" s="33" t="n"/>
-      <c r="M6" s="33" t="n"/>
-      <c r="N6" s="34" t="n"/>
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="35" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="34" t="n"/>
+      <c r="M6" s="34" t="n"/>
+      <c r="N6" s="35" t="n"/>
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
@@ -766,44 +764,44 @@
       <c r="Z6" s="2" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1" s="28">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>假別：</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>事假</t>
         </is>
       </c>
-      <c r="E7" s="36" t="n"/>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="E7" s="37" t="n"/>
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>病假</t>
         </is>
       </c>
-      <c r="G7" s="36" t="n"/>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="G7" s="37" t="n"/>
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>特休</t>
         </is>
       </c>
-      <c r="I7" s="36" t="n"/>
-      <c r="J7" s="35" t="inlineStr">
+      <c r="I7" s="37" t="n"/>
+      <c r="J7" s="36" t="inlineStr">
         <is>
           <t>產/婚/喪  假</t>
         </is>
       </c>
-      <c r="K7" s="37" t="n"/>
-      <c r="L7" s="36" t="n"/>
-      <c r="M7" s="35" t="inlineStr">
+      <c r="K7" s="38" t="n"/>
+      <c r="L7" s="37" t="n"/>
+      <c r="M7" s="36" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="N7" s="36" t="n"/>
+      <c r="N7" s="37" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
@@ -818,20 +816,20 @@
       <c r="Z7" s="2" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1" s="28">
-      <c r="A8" s="32" t="n"/>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="35" t="n"/>
-      <c r="E8" s="36" t="n"/>
-      <c r="F8" s="35" t="n"/>
-      <c r="G8" s="36" t="n"/>
-      <c r="H8" s="35" t="n"/>
-      <c r="I8" s="36" t="n"/>
-      <c r="J8" s="29" t="n"/>
-      <c r="K8" s="37" t="n"/>
-      <c r="L8" s="36" t="n"/>
-      <c r="M8" s="38" t="n"/>
-      <c r="N8" s="36" t="n"/>
+      <c r="A8" s="33" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="35" t="n"/>
+      <c r="D8" s="36" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="37" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="37" t="n"/>
+      <c r="J8" s="30" t="n"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="37" t="n"/>
+      <c r="M8" s="39" t="n"/>
+      <c r="N8" s="37" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
@@ -846,24 +844,24 @@
       <c r="Z8" s="2" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" s="28">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>事由：</t>
         </is>
       </c>
-      <c r="B9" s="30" t="n"/>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="39" t="n"/>
-      <c r="E9" s="30" t="n"/>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="30" t="n"/>
-      <c r="H9" s="30" t="n"/>
-      <c r="I9" s="30" t="n"/>
-      <c r="J9" s="30" t="n"/>
-      <c r="K9" s="30" t="n"/>
-      <c r="L9" s="30" t="n"/>
-      <c r="M9" s="30" t="n"/>
-      <c r="N9" s="31" t="n"/>
+      <c r="B9" s="31" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="40" t="n"/>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
+      <c r="H9" s="31" t="n"/>
+      <c r="I9" s="31" t="n"/>
+      <c r="J9" s="31" t="n"/>
+      <c r="K9" s="31" t="n"/>
+      <c r="L9" s="31" t="n"/>
+      <c r="M9" s="31" t="n"/>
+      <c r="N9" s="32" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n"/>
@@ -878,20 +876,20 @@
       <c r="Z9" s="2" t="n"/>
     </row>
     <row r="10" ht="24.75" customHeight="1" s="28">
-      <c r="A10" s="32" t="n"/>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="34" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="33" t="n"/>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="33" t="n"/>
-      <c r="K10" s="33" t="n"/>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="33" t="n"/>
-      <c r="N10" s="34" t="n"/>
+      <c r="A10" s="33" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="35" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="34" t="n"/>
+      <c r="J10" s="34" t="n"/>
+      <c r="K10" s="34" t="n"/>
+      <c r="L10" s="34" t="n"/>
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="35" t="n"/>
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
@@ -906,12 +904,12 @@
       <c r="Z10" s="2" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1" s="28">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>時間：</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
+      <c r="B11" s="32" t="n"/>
       <c r="C11" s="17" t="n">
         <v>114</v>
       </c>
@@ -944,8 +942,8 @@
           <t>分</t>
         </is>
       </c>
-      <c r="M11" s="35" t="n"/>
-      <c r="N11" s="40" t="inlineStr">
+      <c r="M11" s="36" t="n"/>
+      <c r="N11" s="41" t="inlineStr">
         <is>
           <t>天</t>
         </is>
@@ -964,8 +962,8 @@
       <c r="Z11" s="2" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="28">
-      <c r="A12" s="32" t="n"/>
-      <c r="B12" s="34" t="n"/>
+      <c r="A12" s="33" t="n"/>
+      <c r="B12" s="35" t="n"/>
       <c r="C12" s="17" t="n"/>
       <c r="D12" s="18" t="inlineStr">
         <is>
@@ -996,8 +994,8 @@
           <t>分</t>
         </is>
       </c>
-      <c r="M12" s="41" t="n"/>
-      <c r="N12" s="41" t="n"/>
+      <c r="M12" s="42" t="n"/>
+      <c r="N12" s="42" t="n"/>
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
@@ -1012,36 +1010,36 @@
       <c r="Z12" s="2" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1" s="28">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>簽核：</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="41" t="inlineStr">
         <is>
           <t>執行長/BU主管</t>
         </is>
       </c>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="40" t="inlineStr">
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="38" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="41" t="inlineStr">
         <is>
           <t>人事部</t>
         </is>
       </c>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="37" t="n"/>
-      <c r="J13" s="36" t="n"/>
-      <c r="K13" s="40" t="inlineStr">
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="38" t="n"/>
+      <c r="J13" s="37" t="n"/>
+      <c r="K13" s="41" t="inlineStr">
         <is>
           <t>直屬主管</t>
         </is>
       </c>
-      <c r="L13" s="37" t="n"/>
-      <c r="M13" s="37" t="n"/>
-      <c r="N13" s="36" t="n"/>
+      <c r="L13" s="38" t="n"/>
+      <c r="M13" s="38" t="n"/>
+      <c r="N13" s="37" t="n"/>
       <c r="O13" s="24" t="n"/>
       <c r="P13" s="24" t="n"/>
       <c r="Q13" s="24" t="n"/>
@@ -1056,20 +1054,20 @@
       <c r="Z13" s="24" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1" s="28">
-      <c r="A14" s="42" t="n"/>
-      <c r="B14" s="43" t="n"/>
-      <c r="C14" s="40" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="31" t="n"/>
-      <c r="G14" s="40" t="n"/>
-      <c r="H14" s="30" t="n"/>
-      <c r="I14" s="30" t="n"/>
-      <c r="J14" s="31" t="n"/>
-      <c r="K14" s="40" t="n"/>
-      <c r="L14" s="30" t="n"/>
-      <c r="M14" s="30" t="n"/>
-      <c r="N14" s="31" t="n"/>
+      <c r="A14" s="43" t="n"/>
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="41" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="32" t="n"/>
+      <c r="G14" s="41" t="n"/>
+      <c r="H14" s="31" t="n"/>
+      <c r="I14" s="31" t="n"/>
+      <c r="J14" s="32" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="31" t="n"/>
+      <c r="M14" s="31" t="n"/>
+      <c r="N14" s="32" t="n"/>
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
@@ -1084,14 +1082,14 @@
       <c r="Z14" s="2" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" s="28">
-      <c r="A15" s="42" t="n"/>
-      <c r="B15" s="43" t="n"/>
-      <c r="C15" s="42" t="n"/>
-      <c r="F15" s="43" t="n"/>
-      <c r="G15" s="42" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="42" t="n"/>
-      <c r="N15" s="43" t="n"/>
+      <c r="A15" s="43" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="43" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="43" t="n"/>
+      <c r="J15" s="44" t="n"/>
+      <c r="K15" s="43" t="n"/>
+      <c r="N15" s="44" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
       <c r="Q15" s="2" t="n"/>
@@ -1106,14 +1104,14 @@
       <c r="Z15" s="2" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1" s="28">
-      <c r="A16" s="42" t="n"/>
-      <c r="B16" s="43" t="n"/>
-      <c r="C16" s="42" t="n"/>
-      <c r="F16" s="43" t="n"/>
-      <c r="G16" s="42" t="n"/>
-      <c r="J16" s="43" t="n"/>
-      <c r="K16" s="42" t="n"/>
-      <c r="N16" s="43" t="n"/>
+      <c r="A16" s="43" t="n"/>
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="43" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="43" t="n"/>
+      <c r="J16" s="44" t="n"/>
+      <c r="K16" s="43" t="n"/>
+      <c r="N16" s="44" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
@@ -1128,20 +1126,20 @@
       <c r="Z16" s="2" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1" s="28">
-      <c r="A17" s="32" t="n"/>
-      <c r="B17" s="34" t="n"/>
-      <c r="C17" s="32" t="n"/>
-      <c r="D17" s="33" t="n"/>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="34" t="n"/>
-      <c r="G17" s="32" t="n"/>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="33" t="n"/>
-      <c r="J17" s="34" t="n"/>
-      <c r="K17" s="32" t="n"/>
-      <c r="L17" s="33" t="n"/>
-      <c r="M17" s="33" t="n"/>
-      <c r="N17" s="34" t="n"/>
+      <c r="A17" s="33" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="35" t="n"/>
+      <c r="G17" s="33" t="n"/>
+      <c r="H17" s="34" t="n"/>
+      <c r="I17" s="34" t="n"/>
+      <c r="J17" s="35" t="n"/>
+      <c r="K17" s="33" t="n"/>
+      <c r="L17" s="34" t="n"/>
+      <c r="M17" s="34" t="n"/>
+      <c r="N17" s="35" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
@@ -1162,19 +1160,19 @@
 請假1日內，經由主管簽名即可送交人事行政部。連續請假超過5日(含)以上者，經主管審核後，仍須交由執行長/BU主管簽核。</t>
         </is>
       </c>
-      <c r="B18" s="30" t="n"/>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="30" t="n"/>
-      <c r="F18" s="30" t="n"/>
-      <c r="G18" s="30" t="n"/>
-      <c r="H18" s="30" t="n"/>
-      <c r="I18" s="30" t="n"/>
-      <c r="J18" s="30" t="n"/>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="30" t="n"/>
-      <c r="M18" s="30" t="n"/>
-      <c r="N18" s="30" t="n"/>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n"/>
+      <c r="J18" s="31" t="n"/>
+      <c r="K18" s="31" t="n"/>
+      <c r="L18" s="31" t="n"/>
+      <c r="M18" s="31" t="n"/>
+      <c r="N18" s="31" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
@@ -1292,20 +1290,11 @@
       <c r="Z22" s="2" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1" s="28">
-      <c r="A23" s="2" t="n"/>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
-      <c r="G23" s="2" t="n"/>
-      <c r="H23" s="2" t="n"/>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>請假單</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
@@ -1396,28 +1385,28 @@
       <c r="Z25" s="2" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" s="28">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>請假人：</t>
         </is>
       </c>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="29" t="n"/>
-      <c r="E26" s="30" t="n"/>
-      <c r="F26" s="30" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="30" t="inlineStr">
         <is>
           <t>代理人：</t>
         </is>
       </c>
-      <c r="I26" s="30" t="n"/>
-      <c r="J26" s="31" t="n"/>
-      <c r="K26" s="29" t="n"/>
-      <c r="L26" s="30" t="n"/>
-      <c r="M26" s="30" t="n"/>
-      <c r="N26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="32" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="31" t="n"/>
+      <c r="M26" s="31" t="n"/>
+      <c r="N26" s="32" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
@@ -1432,20 +1421,20 @@
       <c r="Z26" s="2" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" s="28">
-      <c r="A27" s="32" t="n"/>
-      <c r="B27" s="33" t="n"/>
-      <c r="C27" s="34" t="n"/>
-      <c r="D27" s="32" t="n"/>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="33" t="n"/>
-      <c r="G27" s="34" t="n"/>
-      <c r="H27" s="32" t="n"/>
-      <c r="I27" s="33" t="n"/>
-      <c r="J27" s="34" t="n"/>
-      <c r="K27" s="32" t="n"/>
-      <c r="L27" s="33" t="n"/>
-      <c r="M27" s="33" t="n"/>
-      <c r="N27" s="34" t="n"/>
+      <c r="A27" s="33" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="35" t="n"/>
+      <c r="D27" s="33" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="34" t="n"/>
+      <c r="G27" s="35" t="n"/>
+      <c r="H27" s="33" t="n"/>
+      <c r="I27" s="34" t="n"/>
+      <c r="J27" s="35" t="n"/>
+      <c r="K27" s="33" t="n"/>
+      <c r="L27" s="34" t="n"/>
+      <c r="M27" s="34" t="n"/>
+      <c r="N27" s="35" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
@@ -1460,44 +1449,44 @@
       <c r="Z27" s="2" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1" s="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>假別：</t>
         </is>
       </c>
-      <c r="B28" s="30" t="n"/>
-      <c r="C28" s="31" t="n"/>
-      <c r="D28" s="35" t="inlineStr">
+      <c r="B28" s="31" t="n"/>
+      <c r="C28" s="32" t="n"/>
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>事假</t>
         </is>
       </c>
-      <c r="E28" s="36" t="n"/>
-      <c r="F28" s="35" t="inlineStr">
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="36" t="inlineStr">
         <is>
           <t>病假</t>
         </is>
       </c>
-      <c r="G28" s="36" t="n"/>
-      <c r="H28" s="35" t="inlineStr">
+      <c r="G28" s="37" t="n"/>
+      <c r="H28" s="36" t="inlineStr">
         <is>
           <t>特休</t>
         </is>
       </c>
-      <c r="I28" s="36" t="n"/>
-      <c r="J28" s="35" t="inlineStr">
+      <c r="I28" s="37" t="n"/>
+      <c r="J28" s="36" t="inlineStr">
         <is>
           <t>產/婚/喪  假</t>
         </is>
       </c>
-      <c r="K28" s="37" t="n"/>
-      <c r="L28" s="36" t="n"/>
-      <c r="M28" s="35" t="inlineStr">
+      <c r="K28" s="38" t="n"/>
+      <c r="L28" s="37" t="n"/>
+      <c r="M28" s="36" t="inlineStr">
         <is>
           <t>其他</t>
         </is>
       </c>
-      <c r="N28" s="36" t="n"/>
+      <c r="N28" s="37" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
@@ -1512,20 +1501,20 @@
       <c r="Z28" s="2" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" s="28">
-      <c r="A29" s="32" t="n"/>
-      <c r="B29" s="33" t="n"/>
-      <c r="C29" s="34" t="n"/>
-      <c r="D29" s="35" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="35" t="n"/>
-      <c r="G29" s="36" t="n"/>
-      <c r="H29" s="35" t="n"/>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="29" t="n"/>
-      <c r="K29" s="37" t="n"/>
-      <c r="L29" s="36" t="n"/>
-      <c r="M29" s="38" t="n"/>
-      <c r="N29" s="36" t="n"/>
+      <c r="A29" s="33" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="35" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="37" t="n"/>
+      <c r="H29" s="36" t="n"/>
+      <c r="I29" s="37" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="38" t="n"/>
+      <c r="L29" s="37" t="n"/>
+      <c r="M29" s="39" t="n"/>
+      <c r="N29" s="37" t="n"/>
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
@@ -1540,24 +1529,24 @@
       <c r="Z29" s="2" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1" s="28">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>事由：</t>
         </is>
       </c>
-      <c r="B30" s="30" t="n"/>
-      <c r="C30" s="31" t="n"/>
-      <c r="D30" s="39" t="n"/>
-      <c r="E30" s="30" t="n"/>
-      <c r="F30" s="30" t="n"/>
-      <c r="G30" s="30" t="n"/>
-      <c r="H30" s="30" t="n"/>
-      <c r="I30" s="30" t="n"/>
-      <c r="J30" s="30" t="n"/>
-      <c r="K30" s="30" t="n"/>
-      <c r="L30" s="30" t="n"/>
-      <c r="M30" s="30" t="n"/>
-      <c r="N30" s="31" t="n"/>
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="32" t="n"/>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="31" t="n"/>
+      <c r="K30" s="31" t="n"/>
+      <c r="L30" s="31" t="n"/>
+      <c r="M30" s="31" t="n"/>
+      <c r="N30" s="32" t="n"/>
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
@@ -1572,20 +1561,20 @@
       <c r="Z30" s="2" t="n"/>
     </row>
     <row r="31" ht="22.5" customHeight="1" s="28">
-      <c r="A31" s="32" t="n"/>
-      <c r="B31" s="33" t="n"/>
-      <c r="C31" s="34" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="33" t="n"/>
-      <c r="F31" s="33" t="n"/>
-      <c r="G31" s="33" t="n"/>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="33" t="n"/>
-      <c r="J31" s="33" t="n"/>
-      <c r="K31" s="33" t="n"/>
-      <c r="L31" s="33" t="n"/>
-      <c r="M31" s="33" t="n"/>
-      <c r="N31" s="34" t="n"/>
+      <c r="A31" s="33" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
+      <c r="D31" s="33" t="n"/>
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="34" t="n"/>
+      <c r="G31" s="34" t="n"/>
+      <c r="H31" s="34" t="n"/>
+      <c r="I31" s="34" t="n"/>
+      <c r="J31" s="34" t="n"/>
+      <c r="K31" s="34" t="n"/>
+      <c r="L31" s="34" t="n"/>
+      <c r="M31" s="34" t="n"/>
+      <c r="N31" s="35" t="n"/>
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
@@ -1600,12 +1589,12 @@
       <c r="Z31" s="2" t="n"/>
     </row>
     <row r="32" ht="22.5" customHeight="1" s="28">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>時間：</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
+      <c r="B32" s="32" t="n"/>
       <c r="C32" s="17" t="n"/>
       <c r="D32" s="18" t="inlineStr">
         <is>
@@ -1636,8 +1625,8 @@
           <t>分</t>
         </is>
       </c>
-      <c r="M32" s="35" t="n"/>
-      <c r="N32" s="40" t="inlineStr">
+      <c r="M32" s="36" t="n"/>
+      <c r="N32" s="41" t="inlineStr">
         <is>
           <t>天</t>
         </is>
@@ -1656,8 +1645,8 @@
       <c r="Z32" s="2" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="28">
-      <c r="A33" s="32" t="n"/>
-      <c r="B33" s="34" t="n"/>
+      <c r="A33" s="33" t="n"/>
+      <c r="B33" s="35" t="n"/>
       <c r="C33" s="17" t="n"/>
       <c r="D33" s="18" t="inlineStr">
         <is>
@@ -1688,8 +1677,8 @@
           <t>分</t>
         </is>
       </c>
-      <c r="M33" s="41" t="n"/>
-      <c r="N33" s="41" t="n"/>
+      <c r="M33" s="42" t="n"/>
+      <c r="N33" s="42" t="n"/>
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
@@ -1704,36 +1693,36 @@
       <c r="Z33" s="2" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="28">
-      <c r="A34" s="40" t="inlineStr">
+      <c r="A34" s="41" t="inlineStr">
         <is>
           <t>簽核：</t>
         </is>
       </c>
-      <c r="B34" s="31" t="n"/>
-      <c r="C34" s="40" t="inlineStr">
+      <c r="B34" s="32" t="n"/>
+      <c r="C34" s="41" t="inlineStr">
         <is>
           <t>執行長/BU主管</t>
         </is>
       </c>
-      <c r="D34" s="37" t="n"/>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="36" t="n"/>
-      <c r="G34" s="40" t="inlineStr">
+      <c r="D34" s="38" t="n"/>
+      <c r="E34" s="38" t="n"/>
+      <c r="F34" s="37" t="n"/>
+      <c r="G34" s="41" t="inlineStr">
         <is>
           <t>人事部</t>
         </is>
       </c>
-      <c r="H34" s="37" t="n"/>
-      <c r="I34" s="37" t="n"/>
-      <c r="J34" s="36" t="n"/>
-      <c r="K34" s="40" t="inlineStr">
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="38" t="n"/>
+      <c r="J34" s="37" t="n"/>
+      <c r="K34" s="41" t="inlineStr">
         <is>
           <t>直屬主管</t>
         </is>
       </c>
-      <c r="L34" s="37" t="n"/>
-      <c r="M34" s="37" t="n"/>
-      <c r="N34" s="36" t="n"/>
+      <c r="L34" s="38" t="n"/>
+      <c r="M34" s="38" t="n"/>
+      <c r="N34" s="37" t="n"/>
       <c r="O34" s="24" t="n"/>
       <c r="P34" s="24" t="n"/>
       <c r="Q34" s="24" t="n"/>
@@ -1748,20 +1737,20 @@
       <c r="Z34" s="24" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" s="28">
-      <c r="A35" s="42" t="n"/>
-      <c r="B35" s="43" t="n"/>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="40" t="n"/>
-      <c r="H35" s="30" t="n"/>
-      <c r="I35" s="30" t="n"/>
-      <c r="J35" s="31" t="n"/>
-      <c r="K35" s="40" t="n"/>
-      <c r="L35" s="30" t="n"/>
-      <c r="M35" s="30" t="n"/>
-      <c r="N35" s="31" t="n"/>
+      <c r="A35" s="43" t="n"/>
+      <c r="B35" s="44" t="n"/>
+      <c r="C35" s="41" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="41" t="n"/>
+      <c r="H35" s="31" t="n"/>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="32" t="n"/>
+      <c r="K35" s="41" t="n"/>
+      <c r="L35" s="31" t="n"/>
+      <c r="M35" s="31" t="n"/>
+      <c r="N35" s="32" t="n"/>
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
@@ -1776,14 +1765,14 @@
       <c r="Z35" s="2" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1" s="28">
-      <c r="A36" s="42" t="n"/>
-      <c r="B36" s="43" t="n"/>
-      <c r="C36" s="42" t="n"/>
-      <c r="F36" s="43" t="n"/>
-      <c r="G36" s="42" t="n"/>
-      <c r="J36" s="43" t="n"/>
-      <c r="K36" s="42" t="n"/>
-      <c r="N36" s="43" t="n"/>
+      <c r="A36" s="43" t="n"/>
+      <c r="B36" s="44" t="n"/>
+      <c r="C36" s="43" t="n"/>
+      <c r="F36" s="44" t="n"/>
+      <c r="G36" s="43" t="n"/>
+      <c r="J36" s="44" t="n"/>
+      <c r="K36" s="43" t="n"/>
+      <c r="N36" s="44" t="n"/>
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
@@ -1798,14 +1787,14 @@
       <c r="Z36" s="2" t="n"/>
     </row>
     <row r="37" ht="16.5" customHeight="1" s="28">
-      <c r="A37" s="42" t="n"/>
-      <c r="B37" s="43" t="n"/>
-      <c r="C37" s="42" t="n"/>
-      <c r="F37" s="43" t="n"/>
-      <c r="G37" s="42" t="n"/>
-      <c r="J37" s="43" t="n"/>
-      <c r="K37" s="42" t="n"/>
-      <c r="N37" s="43" t="n"/>
+      <c r="A37" s="43" t="n"/>
+      <c r="B37" s="44" t="n"/>
+      <c r="C37" s="43" t="n"/>
+      <c r="F37" s="44" t="n"/>
+      <c r="G37" s="43" t="n"/>
+      <c r="J37" s="44" t="n"/>
+      <c r="K37" s="43" t="n"/>
+      <c r="N37" s="44" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="n"/>
@@ -1820,20 +1809,20 @@
       <c r="Z37" s="2" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" s="28">
-      <c r="A38" s="32" t="n"/>
-      <c r="B38" s="34" t="n"/>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="33" t="n"/>
-      <c r="E38" s="33" t="n"/>
-      <c r="F38" s="34" t="n"/>
-      <c r="G38" s="32" t="n"/>
-      <c r="H38" s="33" t="n"/>
-      <c r="I38" s="33" t="n"/>
-      <c r="J38" s="34" t="n"/>
-      <c r="K38" s="32" t="n"/>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="33" t="n"/>
-      <c r="N38" s="34" t="n"/>
+      <c r="A38" s="33" t="n"/>
+      <c r="B38" s="35" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="34" t="n"/>
+      <c r="E38" s="34" t="n"/>
+      <c r="F38" s="35" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="34" t="n"/>
+      <c r="I38" s="34" t="n"/>
+      <c r="J38" s="35" t="n"/>
+      <c r="K38" s="33" t="n"/>
+      <c r="L38" s="34" t="n"/>
+      <c r="M38" s="34" t="n"/>
+      <c r="N38" s="35" t="n"/>
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n"/>
@@ -1854,19 +1843,19 @@
 請假1日內，經由主管簽名即可送交人事行政部。連續請假超過5日(含)以上者，經主管審核後，仍須交由執行長/BU主管簽核。</t>
         </is>
       </c>
-      <c r="B39" s="30" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="30" t="n"/>
-      <c r="H39" s="30" t="n"/>
-      <c r="I39" s="30" t="n"/>
-      <c r="J39" s="30" t="n"/>
-      <c r="K39" s="30" t="n"/>
-      <c r="L39" s="30" t="n"/>
-      <c r="M39" s="30" t="n"/>
-      <c r="N39" s="30" t="n"/>
+      <c r="B39" s="31" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="31" t="n"/>
+      <c r="I39" s="31" t="n"/>
+      <c r="J39" s="31" t="n"/>
+      <c r="K39" s="31" t="n"/>
+      <c r="L39" s="31" t="n"/>
+      <c r="M39" s="31" t="n"/>
+      <c r="N39" s="31" t="n"/>
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
@@ -28789,7 +28778,7 @@
       <c r="Z1000" s="2" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="60">
     <mergeCell ref="K5:N6"/>
     <mergeCell ref="N32:N33"/>
     <mergeCell ref="C14:F17"/>
@@ -28825,12 +28814,14 @@
     <mergeCell ref="D7:E7"/>
     <mergeCell ref="G14:J17"/>
     <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A2:N2"/>
     <mergeCell ref="M28:N28"/>
     <mergeCell ref="A11:B12"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A23:N23"/>
     <mergeCell ref="M8:N8"/>
     <mergeCell ref="D5:G6"/>
     <mergeCell ref="A26:C27"/>
@@ -28849,7 +28840,7 @@
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="H8:I8"/>
   </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
